--- a/static/xlsx/桃園所最新電話一覽表.xlsx
+++ b/static/xlsx/桃園所最新電話一覽表.xlsx
@@ -42,7 +42,7 @@
     <t>測量主辦</t>
   </si>
   <si>
-    <t>林志明</t>
+    <t>林Ｏ明</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -57,11 +57,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>林雅婷</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>蔡俊傑</t>
+    <t>林Ｏ婷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡Ｏ傑</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -73,7 +73,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>黃怡君</t>
+    <t>黃Ｏ君</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -81,7 +81,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>楊家豪</t>
+    <t>楊Ｏ豪</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -89,49 +89,49 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>莊淑華</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>江冠宇</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>劉詩涵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>吳承翰</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黃佳穎</t>
+    <t>莊Ｏ華</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>江Ｏ宇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉Ｏ涵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳Ｏ翰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃Ｏ穎</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>校對</t>
   </si>
   <si>
-    <t>游柏翰</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>邱雅筑</t>
+    <t>游Ｏ筑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>邱Ｏ廷</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>地價主辦</t>
   </si>
   <si>
-    <t>鄭彥廷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>劉怡安</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>宋宇軒</t>
+    <t>鄭Ｏ安</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉Ｏ軒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>宋Ｏ敏</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -139,11 +139,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>吳淑敏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>朱宗翰</t>
+    <t>吳Ｏ妍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>朱Ｏ思</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -183,7 +183,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>王詩婷</t>
+    <t>王Ｏ宏</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -211,7 +211,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>張子軒</t>
+    <t>張Ｏ彤</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -271,7 +271,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>葉品妍</t>
+    <t>葉Ｏ瑋</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -279,23 +279,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>李志豪</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳思穎</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>劉俊宏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>宋語彤</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>邱家瑋</t>
+    <t>李Ｏ雯</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ恩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉Ｏ樺</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>宋Ｏ雅</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>邱Ｏ貞</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -311,15 +311,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>陳雅雯</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>葉冠廷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>廖怡萱</t>
+    <t>陳Ｏ澤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>葉Ｏ晴</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>廖Ｏ憲</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -332,11 +332,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>蘇承恩</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>張佳樺</t>
+    <t>蘇Ｏ妤</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>張Ｏ偉</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -344,27 +344,27 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>彭柏宇</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>張詩雅</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黃彥宇</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黃淑貞</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>賀宇澤</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>吳子晴</t>
+    <t>彭Ｏ賢</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>張Ｏ銘</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃Ｏ琪</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃Ｏ伶</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>賀Ｏ蓉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳Ｏ博</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -396,7 +396,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>歐陽安</t>
+    <t>歐Ｏ霖</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -408,11 +408,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>李宗憲</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>施品妤</t>
+    <t>李Ｏ翔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>施Ｏ瑜</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -420,17 +420,17 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>李志偉</t>
-  </si>
-  <si>
-    <t>邱思涵</t>
+    <t>李Ｏ強</t>
+  </si>
+  <si>
+    <t>邱Ｏ潔</t>
   </si>
   <si>
     <t>課長</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>謝俊賢</t>
+    <t>謝Ｏ辰</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -438,71 +438,71 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>葉語晴</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黃家銘</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>江雅琪</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>王冠宏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>古怡伶</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳承澤</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>林佳蓉</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>林柏廷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>吳詩晴</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>鄭彥宏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>李淑娟</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>林宇翔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳子瑜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳宗穎</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>馬品萱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>任志強</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>邱思潔</t>
+    <t>葉Ｏ淵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃Ｏ維</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>江Ｏ玲</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>王Ｏ凱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>古Ｏ勳</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ萱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ誠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ芸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳Ｏ泰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄭Ｏ森</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>李Ｏ碩</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ平</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ凱</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ佑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬Ｏ柔</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>任Ｏ諺</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>邱Ｏ銘</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -510,19 +510,19 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>林俊宇</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>林語涵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>葉家宏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>鐘雅芳</t>
+    <t>林Ｏ源</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ康</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>葉Ｏ瑞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘Ｏ欣</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -530,55 +530,55 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>曾冠霖</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳怡璇</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>林承諺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>呂佳琪</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>劉柏叡</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>李詩筠</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>林彥霖</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>謝淑慧</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>鍾宇辰</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黃子涵</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>劉宗樺</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黃品潔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>劉志遠</t>
+    <t>曾Ｏ峰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ佐</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ倫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>呂Ｏ瑋</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉Ｏ霖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>李Ｏ鈞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ軒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>謝Ｏ慶</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鍾Ｏ哲</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃Ｏ達</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉Ｏ源</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃Ｏ安</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>劉Ｏ辰</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -590,11 +590,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>蘇思語</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>邱俊佑</t>
+    <t>蘇Ｏ平</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>邱Ｏ寧</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -604,27 +604,27 @@
     <t>3322101#6153</t>
   </si>
   <si>
-    <t>詹語萱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳家維</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>丘辰</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>李雅玲</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>王冠傑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>林怡潔</t>
+    <t>詹Ｏ謙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ恒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>丘Ｏ和</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>李Ｏ誠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>王Ｏ威</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ翔</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -632,11 +632,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">秘書：吳淑玲  分機:200 專線:(03)369-4788 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>李承勳</t>
+    <t xml:space="preserve">秘書：吳Ｏ鴻  分機:200 專線:(03)369-4788 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李Ｏ凱</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -644,11 +644,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>廖佳萱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>沈柏霖</t>
+    <t>廖Ｏ瑞</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>沈Ｏ陽</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -656,51 +656,51 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>張詩琪</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>林彥博</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>王淑芳</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>段平</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>蘇宇廷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳子萱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>市府便民工作站-蕭宇泰</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>市府便民工作站-邱子豪</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>廖宗諺</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>楊品睿</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>張志成</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳思萱</t>
+    <t>張Ｏ凡</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ樂</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>王Ｏ川</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>段Ｏ風</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>蘇Ｏ雲</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ天</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>市府便民工作站-蕭Ｏ星</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>市府便民工作站-邱Ｏ晨</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>廖Ｏ光</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>楊Ｏ輝</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>張Ｏ泰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ順</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -708,31 +708,31 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>江俊霖</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>主任：陳宗佑  分機:100 專線:(03)369-9779  傳真:(03)369-9777</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>游語柔</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>羅家齊</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>游雅如</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>蕭冠瑋</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>李怡樺</t>
+    <t>江Ｏ福</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>主任：陳Ｏ祥  分機:100 專線:(03)369-9779  傳真:(03)369-9777</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>游Ｏ仁</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>羅Ｏ義</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>游Ｏ禮</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>蕭Ｏ智</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>李Ｏ信</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -740,55 +740,55 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>陳承叡</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>江佳靜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>鍾柏誠</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黃詩芸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>吳彥豪</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>鐘淑婷</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳宇森</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳子芸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳宗澤</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳品碩</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>林志平</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>黃思敏</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>會計室助理:官品宏</t>
+    <t>陳Ｏ忠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>江Ｏ孝</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鍾Ｏ勇</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃Ｏ毅</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>吳Ｏ剛</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘Ｏ健</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ康</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ寧</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ平</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ傑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>黃Ｏ豪</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>會計室助理:官Ｏ華</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -796,47 +796,47 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>人事室助理:趙志康  分機:599</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>會計室主任:宋思瑜 分機300</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>人事室主任:黃俊豪 分機500  專線 369-4699</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳俊凱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>丁語潔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳家佑</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>鄭雅萱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>洪冠賢</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳怡柔</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>林承宇</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>李佳紋</t>
+    <t>人事室助理:趙Ｏ宇  分機:599</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>會計室主任:宋Ｏ涵 分機300</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>人事室主任:黃Ｏ翰 分機500  專線 369-4699</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ穎</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>丁Ｏ筑</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ廷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄭Ｏ軒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>洪Ｏ敏</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ妍</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>林Ｏ思</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>李Ｏ宏</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -844,15 +844,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>簡柏諺</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>陳詩瑜</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>鍾彥銘</t>
+    <t>簡Ｏ彤</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>陳Ｏ瑋</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>鍾Ｏ雯</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
